--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120285916</v>
+        <v>120285917</v>
       </c>
       <c r="B7" t="n">
         <v>91272</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769364</v>
+        <v>769255</v>
       </c>
       <c r="R7" t="n">
-        <v>7084940</v>
+        <v>7084931</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120285917</v>
+        <v>120285916</v>
       </c>
       <c r="B8" t="n">
         <v>91272</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>769255</v>
+        <v>769364</v>
       </c>
       <c r="R8" t="n">
-        <v>7084931</v>
+        <v>7084940</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120285917</v>
+        <v>120285916</v>
       </c>
       <c r="B7" t="n">
         <v>91272</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769255</v>
+        <v>769364</v>
       </c>
       <c r="R7" t="n">
-        <v>7084931</v>
+        <v>7084940</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120285916</v>
+        <v>120285917</v>
       </c>
       <c r="B8" t="n">
         <v>91272</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>769364</v>
+        <v>769255</v>
       </c>
       <c r="R8" t="n">
-        <v>7084940</v>
+        <v>7084931</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,6 +1386,260 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120552815</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>112</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>769447</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7084700</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>granlåga mossbevuxen</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga mossbevuxen</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120552814</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>769423</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7084945</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack äldre gran norrsidan</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Äldre gran</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre gran</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -2326,7 +2326,7 @@
         <v>120864237</v>
       </c>
       <c r="B17" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121098711</v>
+        <v>121098748</v>
       </c>
       <c r="B18" t="n">
-        <v>57364</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,16 +2467,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2484,12 +2484,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2499,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769388</v>
+        <v>769417</v>
       </c>
       <c r="R18" t="n">
-        <v>7084828</v>
+        <v>7084685</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121098715</v>
+        <v>121098723</v>
       </c>
       <c r="B19" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2609,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769434</v>
+        <v>769416</v>
       </c>
       <c r="R19" t="n">
-        <v>7084802</v>
+        <v>7084666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,10 +2675,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121098723</v>
+        <v>121098715</v>
       </c>
       <c r="B20" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2719,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769416</v>
+        <v>769434</v>
       </c>
       <c r="R20" t="n">
-        <v>7084666</v>
+        <v>7084802</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121098748</v>
+        <v>121098711</v>
       </c>
       <c r="B21" t="n">
-        <v>57348</v>
+        <v>57367</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,16 +2801,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2814,16 +2818,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769417</v>
+        <v>769388</v>
       </c>
       <c r="R21" t="n">
-        <v>7084685</v>
+        <v>7084828</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2898,7 @@
         <v>121120111</v>
       </c>
       <c r="B22" t="n">
-        <v>91127</v>
+        <v>91137</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121169079</v>
+        <v>121169086</v>
       </c>
       <c r="B23" t="n">
-        <v>90652</v>
+        <v>57367</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3013,38 +3013,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769351</v>
+        <v>769343</v>
       </c>
       <c r="R23" t="n">
-        <v>7084805</v>
+        <v>7084662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,11 +3082,21 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3087,26 +3105,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Granlåga sågad i 3 delar vid vägkant</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga sågad i 3 delar vid vägkant</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3123,10 +3121,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121169086</v>
+        <v>121169088</v>
       </c>
       <c r="B24" t="n">
-        <v>57364</v>
+        <v>91137</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3135,46 +3133,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769343</v>
+        <v>769441</v>
       </c>
       <c r="R24" t="n">
-        <v>7084662</v>
+        <v>7084723</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3204,19 +3194,14 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:15</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3227,6 +3212,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3243,10 +3248,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121169088</v>
+        <v>121169079</v>
       </c>
       <c r="B25" t="n">
-        <v>91127</v>
+        <v>90662</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3255,25 +3260,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3283,10 +3288,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769441</v>
+        <v>769351</v>
       </c>
       <c r="R25" t="n">
-        <v>7084723</v>
+        <v>7084805</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3321,11 +3326,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga sågad i 3 delar vid vägkant</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga sågad i 3 delar vid vägkant</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
         <v>121169112</v>
       </c>
       <c r="B26" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>121347151</v>
       </c>
       <c r="B27" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121098748</v>
+        <v>121098711</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,16 +2467,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2484,16 +2484,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2503,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769417</v>
+        <v>769388</v>
       </c>
       <c r="R18" t="n">
-        <v>7084685</v>
+        <v>7084828</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,7 +2561,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121098723</v>
+        <v>121098715</v>
       </c>
       <c r="B19" t="n">
         <v>57367</v>
@@ -2613,10 +2609,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769416</v>
+        <v>769434</v>
       </c>
       <c r="R19" t="n">
-        <v>7084666</v>
+        <v>7084802</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2675,10 +2671,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121098715</v>
+        <v>121098748</v>
       </c>
       <c r="B20" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2691,16 +2687,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2708,12 +2704,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769434</v>
+        <v>769417</v>
       </c>
       <c r="R20" t="n">
-        <v>7084802</v>
+        <v>7084685</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121098711</v>
+        <v>121098723</v>
       </c>
       <c r="B21" t="n">
         <v>57367</v>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769388</v>
+        <v>769416</v>
       </c>
       <c r="R21" t="n">
-        <v>7084828</v>
+        <v>7084666</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3001,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121169086</v>
+        <v>121169079</v>
       </c>
       <c r="B23" t="n">
-        <v>57367</v>
+        <v>90662</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3013,46 +3013,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769343</v>
+        <v>769351</v>
       </c>
       <c r="R23" t="n">
-        <v>7084662</v>
+        <v>7084805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,21 +3074,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3105,6 +3087,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Granlåga sågad i 3 delar vid vägkant</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga sågad i 3 delar vid vägkant</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3121,10 +3123,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121169088</v>
+        <v>121169112</v>
       </c>
       <c r="B24" t="n">
-        <v>91137</v>
+        <v>57367</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3133,38 +3135,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769441</v>
+        <v>769422</v>
       </c>
       <c r="R24" t="n">
-        <v>7084723</v>
+        <v>7084728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3201,7 +3208,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Hänssynssnitsel SCA</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3225,12 +3232,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granhögstubbe, knäckt med bohål</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granhögstubbe, knäckt med bohål</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3248,10 +3255,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121169079</v>
+        <v>121169088</v>
       </c>
       <c r="B25" t="n">
-        <v>90662</v>
+        <v>91137</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3260,25 +3267,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3288,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769351</v>
+        <v>769441</v>
       </c>
       <c r="R25" t="n">
-        <v>7084805</v>
+        <v>7084723</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3326,6 +3333,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3347,12 +3359,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Granlåga sågad i 3 delar vid vägkant</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga sågad i 3 delar vid vägkant</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3370,7 +3382,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121169112</v>
+        <v>121169086</v>
       </c>
       <c r="B26" t="n">
         <v>57367</v>
@@ -3404,21 +3416,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769422</v>
+        <v>769343</v>
       </c>
       <c r="R26" t="n">
-        <v>7084728</v>
+        <v>7084662</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3448,14 +3463,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hänssynssnitsel SCA</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3466,26 +3486,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt med bohål</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe, knäckt med bohål</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121098711</v>
+        <v>121098715</v>
       </c>
       <c r="B18" t="n">
         <v>57367</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769388</v>
+        <v>769434</v>
       </c>
       <c r="R18" t="n">
-        <v>7084828</v>
+        <v>7084802</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,7 +2561,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121098715</v>
+        <v>121098723</v>
       </c>
       <c r="B19" t="n">
         <v>57367</v>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769434</v>
+        <v>769416</v>
       </c>
       <c r="R19" t="n">
-        <v>7084802</v>
+        <v>7084666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121098723</v>
+        <v>121098711</v>
       </c>
       <c r="B21" t="n">
         <v>57367</v>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769416</v>
+        <v>769388</v>
       </c>
       <c r="R21" t="n">
-        <v>7084666</v>
+        <v>7084828</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2898,7 @@
         <v>121120111</v>
       </c>
       <c r="B22" t="n">
-        <v>91137</v>
+        <v>91149</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121169079</v>
+        <v>121169112</v>
       </c>
       <c r="B23" t="n">
-        <v>90662</v>
+        <v>57367</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3013,38 +3013,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769351</v>
+        <v>769422</v>
       </c>
       <c r="R23" t="n">
-        <v>7084805</v>
+        <v>7084728</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3079,6 +3084,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hänssynssnitsel SCA</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3100,12 +3110,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Granlåga sågad i 3 delar vid vägkant</t>
+          <t>Granhögstubbe, knäckt med bohål</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga sågad i 3 delar vid vägkant</t>
+          <t>Picea abies # Granhögstubbe, knäckt med bohål</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3123,7 +3133,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121169112</v>
+        <v>121169086</v>
       </c>
       <c r="B24" t="n">
         <v>57367</v>
@@ -3157,21 +3167,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769422</v>
+        <v>769343</v>
       </c>
       <c r="R24" t="n">
-        <v>7084728</v>
+        <v>7084662</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3201,14 +3214,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hänssynssnitsel SCA</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3219,26 +3237,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt med bohål</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe, knäckt med bohål</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3258,7 +3256,7 @@
         <v>121169088</v>
       </c>
       <c r="B25" t="n">
-        <v>91137</v>
+        <v>91149</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3382,10 +3380,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121169086</v>
+        <v>121169079</v>
       </c>
       <c r="B26" t="n">
-        <v>57367</v>
+        <v>90674</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3394,46 +3392,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769343</v>
+        <v>769351</v>
       </c>
       <c r="R26" t="n">
-        <v>7084662</v>
+        <v>7084805</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,21 +3453,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3486,6 +3466,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Granlåga sågad i 3 delar vid vägkant</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga sågad i 3 delar vid vägkant</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3505,7 +3505,7 @@
         <v>121347151</v>
       </c>
       <c r="B27" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121098715</v>
+        <v>121098711</v>
       </c>
       <c r="B18" t="n">
         <v>57367</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769434</v>
+        <v>769388</v>
       </c>
       <c r="R18" t="n">
-        <v>7084802</v>
+        <v>7084828</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,10 +2561,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121098723</v>
+        <v>121098748</v>
       </c>
       <c r="B19" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2577,16 +2577,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2594,12 +2594,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2609,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769416</v>
+        <v>769417</v>
       </c>
       <c r="R19" t="n">
-        <v>7084666</v>
+        <v>7084685</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,10 +2675,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121098748</v>
+        <v>121098715</v>
       </c>
       <c r="B20" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2687,16 +2691,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2704,16 +2708,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769417</v>
+        <v>769434</v>
       </c>
       <c r="R20" t="n">
-        <v>7084685</v>
+        <v>7084802</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121098711</v>
+        <v>121098723</v>
       </c>
       <c r="B21" t="n">
         <v>57367</v>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769388</v>
+        <v>769416</v>
       </c>
       <c r="R21" t="n">
-        <v>7084828</v>
+        <v>7084666</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2898,7 @@
         <v>121120111</v>
       </c>
       <c r="B22" t="n">
-        <v>91149</v>
+        <v>91150</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121169112</v>
+        <v>121169086</v>
       </c>
       <c r="B23" t="n">
         <v>57367</v>
@@ -3035,21 +3035,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769422</v>
+        <v>769343</v>
       </c>
       <c r="R23" t="n">
-        <v>7084728</v>
+        <v>7084662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3079,14 +3082,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hänssynssnitsel SCA</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,26 +3105,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt med bohål</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe, knäckt med bohål</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3133,7 +3121,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121169086</v>
+        <v>121169112</v>
       </c>
       <c r="B24" t="n">
         <v>57367</v>
@@ -3167,24 +3155,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769343</v>
+        <v>769422</v>
       </c>
       <c r="R24" t="n">
-        <v>7084662</v>
+        <v>7084728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3214,19 +3199,14 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:15</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hänssynssnitsel SCA</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,6 +3217,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Granhögstubbe, knäckt med bohål</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe, knäckt med bohål</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3253,10 +3253,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121169088</v>
+        <v>121169079</v>
       </c>
       <c r="B25" t="n">
-        <v>91149</v>
+        <v>90675</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3265,25 +3265,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769441</v>
+        <v>769351</v>
       </c>
       <c r="R25" t="n">
-        <v>7084723</v>
+        <v>7084805</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,11 +3331,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3357,12 +3352,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga sågad i 3 delar vid vägkant</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga sågad i 3 delar vid vägkant</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3380,10 +3375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121169079</v>
+        <v>121169088</v>
       </c>
       <c r="B26" t="n">
-        <v>90674</v>
+        <v>91150</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3392,25 +3387,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3420,10 +3415,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769351</v>
+        <v>769441</v>
       </c>
       <c r="R26" t="n">
-        <v>7084805</v>
+        <v>7084723</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3458,6 +3453,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Granlåga sågad i 3 delar vid vägkant</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga sågad i 3 delar vid vägkant</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121098711</v>
+        <v>121098748</v>
       </c>
       <c r="B18" t="n">
-        <v>57367</v>
+        <v>57354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,16 +2467,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2484,12 +2484,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2499,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769388</v>
+        <v>769417</v>
       </c>
       <c r="R18" t="n">
-        <v>7084828</v>
+        <v>7084685</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121098748</v>
+        <v>121098715</v>
       </c>
       <c r="B19" t="n">
-        <v>57351</v>
+        <v>57370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2577,16 +2581,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2594,16 +2598,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769417</v>
+        <v>769434</v>
       </c>
       <c r="R19" t="n">
-        <v>7084685</v>
+        <v>7084802</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121098715</v>
+        <v>121098711</v>
       </c>
       <c r="B20" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769434</v>
+        <v>769388</v>
       </c>
       <c r="R20" t="n">
-        <v>7084802</v>
+        <v>7084828</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
         <v>121098723</v>
       </c>
       <c r="B21" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>121120111</v>
       </c>
       <c r="B22" t="n">
-        <v>91150</v>
+        <v>91153</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121169086</v>
+        <v>121169088</v>
       </c>
       <c r="B23" t="n">
-        <v>57367</v>
+        <v>91153</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3013,46 +3013,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769343</v>
+        <v>769441</v>
       </c>
       <c r="R23" t="n">
-        <v>7084662</v>
+        <v>7084723</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,19 +3074,14 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:15</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3105,6 +3092,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3121,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121169112</v>
+        <v>121169079</v>
       </c>
       <c r="B24" t="n">
-        <v>57367</v>
+        <v>90678</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3133,43 +3140,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769422</v>
+        <v>769351</v>
       </c>
       <c r="R24" t="n">
-        <v>7084728</v>
+        <v>7084805</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3204,11 +3206,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hänssynssnitsel SCA</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3230,12 +3227,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt med bohål</t>
+          <t>Granlåga sågad i 3 delar vid vägkant</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt med bohål</t>
+          <t>Picea abies # Granlåga sågad i 3 delar vid vägkant</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3253,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121169079</v>
+        <v>121169086</v>
       </c>
       <c r="B25" t="n">
-        <v>90675</v>
+        <v>57370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3265,38 +3262,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769351</v>
+        <v>769343</v>
       </c>
       <c r="R25" t="n">
-        <v>7084805</v>
+        <v>7084662</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3326,11 +3331,21 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3339,26 +3354,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Granlåga sågad i 3 delar vid vägkant</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga sågad i 3 delar vid vägkant</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3375,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121169088</v>
+        <v>121169112</v>
       </c>
       <c r="B26" t="n">
-        <v>91150</v>
+        <v>57370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3387,38 +3382,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769441</v>
+        <v>769422</v>
       </c>
       <c r="R26" t="n">
-        <v>7084723</v>
+        <v>7084728</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Hänssynssnitsel SCA</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granhögstubbe, knäckt med bohål</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granhögstubbe, knäckt med bohål</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3505,7 +3505,7 @@
         <v>121347151</v>
       </c>
       <c r="B27" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -3001,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121169088</v>
+        <v>121169112</v>
       </c>
       <c r="B23" t="n">
-        <v>91153</v>
+        <v>57370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3013,38 +3013,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769441</v>
+        <v>769422</v>
       </c>
       <c r="R23" t="n">
-        <v>7084723</v>
+        <v>7084728</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3081,7 +3086,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Hänssynssnitsel SCA</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3105,12 +3110,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granhögstubbe, knäckt med bohål</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granhögstubbe, knäckt med bohål</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3128,10 +3133,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121169079</v>
+        <v>121169088</v>
       </c>
       <c r="B24" t="n">
-        <v>90678</v>
+        <v>91153</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3140,25 +3145,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +3173,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769351</v>
+        <v>769441</v>
       </c>
       <c r="R24" t="n">
-        <v>7084805</v>
+        <v>7084723</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3206,6 +3211,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3227,12 +3237,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Granlåga sågad i 3 delar vid vägkant</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga sågad i 3 delar vid vägkant</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3250,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121169086</v>
+        <v>121169079</v>
       </c>
       <c r="B25" t="n">
-        <v>57370</v>
+        <v>90678</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3262,46 +3272,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769343</v>
+        <v>769351</v>
       </c>
       <c r="R25" t="n">
-        <v>7084662</v>
+        <v>7084805</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,21 +3333,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3354,6 +3346,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Granlåga sågad i 3 delar vid vägkant</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga sågad i 3 delar vid vägkant</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3370,7 +3382,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121169112</v>
+        <v>121169086</v>
       </c>
       <c r="B26" t="n">
         <v>57370</v>
@@ -3404,21 +3416,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769422</v>
+        <v>769343</v>
       </c>
       <c r="R26" t="n">
-        <v>7084728</v>
+        <v>7084662</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3448,14 +3463,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hänssynssnitsel SCA</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3466,26 +3486,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt med bohål</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe, knäckt med bohål</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -3004,7 +3004,7 @@
         <v>121169112</v>
       </c>
       <c r="B23" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>121169088</v>
       </c>
       <c r="B24" t="n">
-        <v>91153</v>
+        <v>91159</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>121169079</v>
       </c>
       <c r="B25" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>121169086</v>
       </c>
       <c r="B26" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>121347151</v>
       </c>
       <c r="B27" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -3505,7 +3505,7 @@
         <v>121347151</v>
       </c>
       <c r="B27" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3641,6 +3641,127 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120552819</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91410</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>769418</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7084943</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen nedbruten</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga mossbevuxen nedbruten</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -3646,7 +3646,7 @@
         <v>120552819</v>
       </c>
       <c r="B28" t="n">
-        <v>91410</v>
+        <v>91570</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -3646,12 +3646,7 @@
         <v>120552819</v>
       </c>
       <c r="B28" t="n">
-        <v>91570</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91624</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -3646,7 +3646,7 @@
         <v>120552819</v>
       </c>
       <c r="B28" t="n">
-        <v>91624</v>
+        <v>91631</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -3646,7 +3646,7 @@
         <v>120552819</v>
       </c>
       <c r="B28" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -3646,7 +3646,7 @@
         <v>120552819</v>
       </c>
       <c r="B28" t="n">
-        <v>91635</v>
+        <v>91639</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 46142-2024 artfynd.xlsx
+++ b/artfynd/A 46142-2024 artfynd.xlsx
@@ -3646,7 +3646,7 @@
         <v>120552819</v>
       </c>
       <c r="B28" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
